--- a/results/pipeline_run.xlsx
+++ b/results/pipeline_run.xlsx
@@ -38,7 +38,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +60,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -85,6 +90,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -566,7 +574,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -616,7 +624,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -666,7 +674,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -681,9 +689,9 @@
           <t>news</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -711,12 +719,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>borderline_morphology:39.8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -766,7 +774,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -816,7 +824,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -866,7 +874,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -881,9 +889,9 @@
           <t>news</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -911,12 +919,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>borderline_morphology:38.2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -966,7 +974,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1024,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1074,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1124,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1131,9 +1139,9 @@
           <t>news</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>reject</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1161,12 +1169,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>low_morphology_score:1.5&lt;15.0</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1220,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1270,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1277,9 +1285,9 @@
           <t>ocr</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1307,12 +1315,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>borderline_morphology:44.0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1370,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1420,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1470,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1477,9 +1485,9 @@
           <t>ocr</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>reject</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1507,12 +1515,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>low_morphology_score:2.5&lt;15.0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1570,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1577,9 +1585,9 @@
           <t>ocr</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1607,12 +1615,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>borderline_morphology:41.3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1670,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1677,9 +1685,9 @@
           <t>asr</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1707,12 +1715,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>borderline_morphology:35.8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1770,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1820,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1870,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1920,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1970,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -1977,9 +1985,9 @@
           <t>asr</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2007,12 +2015,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>borderline_morphology:42.6</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -2027,9 +2035,9 @@
           <t>asr</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2057,12 +2065,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>borderline_morphology:42.2</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2085,7 +2093,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Sinhala Quality Pipeline — Run Summary</t>
         </is>
@@ -2145,7 +2153,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -2155,48 +2163,58 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  review</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>By source:</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  asr</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>8</v>
-      </c>
+          <t>By source:</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  news</t>
+          <t xml:space="preserve">  asr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  news</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ocr</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
         <v>8</v>
       </c>
     </row>

--- a/results/pipeline_run.xlsx
+++ b/results/pipeline_run.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -639,9 +639,9 @@
           <t>news</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>reject</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>semantic_duplicate_of:news_001:1.00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1189,9 +1189,9 @@
           <t>news</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>reject</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>no_sinhala_content</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1635,9 +1635,9 @@
           <t>ocr</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>accept</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>reject</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>tentative_accept:no_rejection_signals</t>
+          <t>no_sinhala_content</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score</t>
+          <t>linguistic.unicode_normalize → quality.exact_hash_dedup → quality.morphology_score → quality.cross_register_overlap</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
